--- a/Guru_Punvaanii_Complete_SEO_Audit_Report.xlsx
+++ b/Guru_Punvaanii_Complete_SEO_Audit_Report.xlsx
@@ -548,13 +548,13 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - EXECUTIVE SUMMARY</t>
+          <t>GURU PUNVAANII PROPERTIES - EXECUTIVE SUMMARY (Generated: 2026-09-19 11:54:04)</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>OPEN (2-Hop Active)</t>
         </is>
       </c>
     </row>
@@ -766,17 +766,17 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>1 Hour</t>
+          <t>0 Min</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Enforces Strict-Transport-Security on all HTTPS endpoints.</t>
+          <t>Strict-Transport-Security (max-age=31536000) active sitewide.</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>RESOLVED</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - TECHNICAL SEO</t>
+          <t>GURU PUNVAANII PROPERTIES - TECHNICAL SEO (Generated: 2026-09-19 11:54:04)</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - ON-PAGE SEO</t>
+          <t>GURU PUNVAANII PROPERTIES - ON-PAGE SEO (Generated: 2026-09-19 11:54:04)</t>
         </is>
       </c>
     </row>
@@ -7886,7 +7886,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - SCHEMA &amp; STRUCTURED DATA</t>
+          <t>GURU PUNVAANII PROPERTIES - SCHEMA &amp; STRUCTURED DATA (Generated: 2026-09-19 11:54:04)</t>
         </is>
       </c>
     </row>
@@ -11279,7 +11279,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - IMAGE SEO &amp; ALT TAGS</t>
+          <t>GURU PUNVAANII PROPERTIES - IMAGE SEO &amp; ALT TAGS (Generated: 2026-09-19 11:54:04)</t>
         </is>
       </c>
     </row>
@@ -11337,7 +11337,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - REDIRECTS &amp; CRAWL</t>
+          <t>GURU PUNVAANII PROPERTIES - REDIRECTS &amp; CRAWL (Generated: 2026-09-19 11:54:04)</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - OFF-PAGE &amp; CITATIONS</t>
+          <t>GURU PUNVAANII PROPERTIES - OFF-PAGE &amp; CITATIONS (Generated: 2026-09-19 11:54:04)</t>
         </is>
       </c>
     </row>
@@ -11717,7 +11717,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - 30-DAY ACTION PLAN</t>
+          <t>GURU PUNVAANII PROPERTIES - 30-DAY ACTION PLAN (Generated: 2026-09-19 11:54:04)</t>
         </is>
       </c>
     </row>

--- a/Guru_Punvaanii_Complete_SEO_Audit_Report.xlsx
+++ b/Guru_Punvaanii_Complete_SEO_Audit_Report.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Image SEO &amp; Alt Tags" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GSC &amp; GA4 Live Data" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30-Day Action Plan" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Performance Tracking" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +550,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - EXECUTIVE SUMMARY (Updated: 2026-09-24 16:14:14)</t>
+          <t>GURU PUNVAANII PROPERTIES - EXECUTIVE SUMMARY (Updated: 2026-09-26 12:50:54)</t>
         </is>
       </c>
     </row>
@@ -831,12 +832,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>5,295 Users</t>
+          <t>5,317 Users</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>6,197 Sessions</t>
+          <t>6,226 Sessions</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -882,7 +883,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - TECHNICAL SEO (Updated: 2026-09-24 16:14:14)</t>
+          <t>GURU PUNVAANII PROPERTIES - TECHNICAL SEO (Updated: 2026-09-26 12:50:54)</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4918,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - ON-PAGE SEO (Updated: 2026-09-24 16:14:14)</t>
+          <t>GURU PUNVAANII PROPERTIES - ON-PAGE SEO (Updated: 2026-09-26 12:50:54)</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8842,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - SCHEMA &amp; STRUCTURED DATA (Updated: 2026-09-24 16:14:14)</t>
+          <t>GURU PUNVAANII PROPERTIES - SCHEMA &amp; STRUCTURED DATA (Updated: 2026-09-26 12:50:54)</t>
         </is>
       </c>
     </row>
@@ -12678,7 +12679,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - CORE WEB VITALS (Updated: 2026-09-24 16:14:14)</t>
+          <t>GURU PUNVAANII PROPERTIES - CORE WEB VITALS (Updated: 2026-09-26 12:50:54)</t>
         </is>
       </c>
     </row>
@@ -16797,7 +16798,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - IMAGE SEO &amp; ALT TAGS (Updated: 2026-09-24 16:14:14)</t>
+          <t>GURU PUNVAANII PROPERTIES - IMAGE SEO &amp; ALT TAGS (Updated: 2026-09-26 12:50:54)</t>
         </is>
       </c>
     </row>
@@ -16983,7 +16984,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - GSC &amp; GA4 LIVE DATA (Updated: 2026-09-24 16:14:14)</t>
+          <t>GURU PUNVAANII PROPERTIES - GSC &amp; GA4 LIVE DATA (Updated: 2026-09-26 12:50:54)</t>
         </is>
       </c>
     </row>
@@ -17607,14 +17608,14 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1023</v>
+        <v>1030</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1546</v>
+        <v>1555</v>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2063 Views</t>
+          <t>2082 Views</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -17635,14 +17636,14 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>996 Views</t>
+          <t>999 Views</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -17663,14 +17664,14 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>949 Views</t>
+          <t>951 Views</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -17698,7 +17699,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>896 Views</t>
+          <t>899 Views</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -17831,14 +17832,14 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>287 Views</t>
+          <t>292 Views</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -17915,14 +17916,14 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>238 Views</t>
+          <t>242 Views</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -18055,14 +18056,14 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>141 Views</t>
+          <t>143 Views</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -18111,14 +18112,14 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>121 Views</t>
+          <t>123 Views</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -18146,7 +18147,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>116 Views</t>
+          <t>121 Views</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -18167,10 +18168,10 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>3002</v>
+        <v>3010</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>3791</v>
+        <v>3809</v>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
@@ -18195,10 +18196,10 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
@@ -18223,10 +18224,10 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
@@ -18279,10 +18280,10 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
@@ -18303,14 +18304,14 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>Cross-network</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
@@ -18331,14 +18332,14 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Cross-network</t>
+          <t>Referral</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
@@ -18408,7 +18409,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - 30-DAY ACTION PLAN (Updated: 2026-09-24 16:14:14)</t>
+          <t>GURU PUNVAANII PROPERTIES - 30-DAY ACTION PLAN (Updated: 2026-09-26 12:50:54)</t>
         </is>
       </c>
     </row>
@@ -18825,4 +18826,133 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>GURU PUNVAANII PROPERTIES - WEEKLY PERFORMANCE TRACKING (Updated: 2026-09-26 12:50:54)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Mobile Performance</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Desktop Performance</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Mobile LCP</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Mobile CLS</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Mobile TBT</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Recorded Date</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Status / Trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>27th Sept - 3rd Oct</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>97/100</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>78/100</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>78/100</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>2.4 s</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>120 ms</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-26 12:49:34</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Guru_Punvaanii_Complete_SEO_Audit_Report.xlsx
+++ b/Guru_Punvaanii_Complete_SEO_Audit_Report.xlsx
@@ -550,7 +550,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - EXECUTIVE SUMMARY (Updated: 2026-09-26 12:50:54)</t>
+          <t>GURU PUNVAANII PROPERTIES - EXECUTIVE SUMMARY (Updated: 2026-09-29 12:05:18)</t>
         </is>
       </c>
     </row>
@@ -805,12 +805,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3,282 Clicks</t>
+          <t>3,319 Clicks</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>328,674 Impressions</t>
+          <t>318,659 Impressions</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>5,317 Users</t>
+          <t>5,482 Users</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>6,226 Sessions</t>
+          <t>6,439 Sessions</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - TECHNICAL SEO (Updated: 2026-09-26 12:50:54)</t>
+          <t>GURU PUNVAANII PROPERTIES - TECHNICAL SEO (Updated: 2026-09-29 12:05:18)</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - ON-PAGE SEO (Updated: 2026-09-26 12:50:54)</t>
+          <t>GURU PUNVAANII PROPERTIES - ON-PAGE SEO (Updated: 2026-09-29 12:05:18)</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - SCHEMA &amp; STRUCTURED DATA (Updated: 2026-09-26 12:50:54)</t>
+          <t>GURU PUNVAANII PROPERTIES - SCHEMA &amp; STRUCTURED DATA (Updated: 2026-09-29 12:05:18)</t>
         </is>
       </c>
     </row>
@@ -12679,7 +12679,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - CORE WEB VITALS (Updated: 2026-09-26 12:50:54)</t>
+          <t>GURU PUNVAANII PROPERTIES - CORE WEB VITALS (Updated: 2026-09-29 12:05:18)</t>
         </is>
       </c>
     </row>
@@ -16798,7 +16798,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - IMAGE SEO &amp; ALT TAGS (Updated: 2026-09-26 12:50:54)</t>
+          <t>GURU PUNVAANII PROPERTIES - IMAGE SEO &amp; ALT TAGS (Updated: 2026-09-29 12:05:18)</t>
         </is>
       </c>
     </row>
@@ -16984,7 +16984,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - GSC &amp; GA4 LIVE DATA (Updated: 2026-09-26 12:50:54)</t>
+          <t>GURU PUNVAANII PROPERTIES - GSC &amp; GA4 LIVE DATA (Updated: 2026-09-29 12:05:18)</t>
         </is>
       </c>
     </row>
@@ -17032,14 +17032,14 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>3282</v>
+        <v>3319</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>328674</v>
+        <v>318659</v>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -17060,14 +17060,14 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>833</v>
+        <v>796</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>85906</v>
+        <v>85812</v>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -17088,14 +17088,14 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>395</v>
+        <v>429</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>41.27%</t>
+          <t>40.33%</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
@@ -17114,18 +17114,18 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2028</v>
+        <v>1718</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>5.42%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -17136,22 +17136,22 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>kaveri online services</t>
+          <t>guru punvaanii</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>41104</v>
+        <v>129</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>51.16%</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -17162,22 +17162,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>guru punvaanii</t>
+          <t>gurupunvaanii</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>56.67%</t>
+          <t>38.73%</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -17188,22 +17188,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>gurupunvaanii</t>
+          <t>igr karnataka</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>143</v>
+        <v>1989</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>40.56%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -17214,22 +17214,22 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>kaveri online</t>
+          <t>kaveri online services</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>65853</v>
+        <v>30304</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -17240,18 +17240,18 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>igr karnataka</t>
+          <t>is south facing house good</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1630</v>
+        <v>928</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>5.17%</t>
         </is>
       </c>
       <c r="F11" s="6" t="n">
@@ -17266,22 +17266,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>is south facing house good</t>
+          <t>south facing house vastu good or bad</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1070</v>
+        <v>1176</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -17292,22 +17292,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>south facing house vastu good or bad</t>
+          <t>kaveri online</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1313</v>
+        <v>46470</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>3.81%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -17318,22 +17318,22 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>kaveri online services portal</t>
+          <t>south facing house is good or bad</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>7020</v>
+        <v>484</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>7.44%</t>
         </is>
       </c>
       <c r="F14" s="6" t="n">
-        <v>7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -17344,22 +17344,22 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>south facing house is good or bad</t>
+          <t>guru punvaanii properties</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>584</v>
+        <v>421</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>6.34%</t>
+          <t>5.46%</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -17370,22 +17370,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>is south facing house good as per vastu</t>
+          <t>guru punvaanii elegance</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>990</v>
+        <v>208</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>2.42%</t>
+          <t>10.58%</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -17396,22 +17396,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>guru punvaanii properties</t>
+          <t>kaveri online services portal</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>387</v>
+        <v>5419</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>5.17%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -17422,22 +17422,22 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>guru punvaanii elegance</t>
+          <t>is south facing house good as per vastu</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>182</v>
+        <v>826</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>9.89%</t>
+          <t>2.54%</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -17448,22 +17448,22 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>north facing house good or bad</t>
+          <t>e khata status</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1312</v>
+        <v>2753</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2.2</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -17474,22 +17474,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>south face house is good or bad</t>
+          <t>south facing house good or bad</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
         <v>16</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>340</v>
+        <v>373</v>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>4.71%</t>
+          <t>4.29%</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -17500,22 +17500,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>guru punvaani</t>
+          <t>north facing house good or bad</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
         <v>14</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>27</v>
+        <v>1131</v>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>51.85%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -17526,22 +17526,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>is north facing house good</t>
+          <t>guru punvaani</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>532</v>
+        <v>26</v>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -17552,22 +17552,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>shyam residency</t>
+          <t>is north facing house good</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>119</v>
+        <v>460</v>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>11.76%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
-        <v>5.3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -17578,22 +17578,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>south facing house</t>
+          <t>south face house is good or bad</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1600</v>
+        <v>276</v>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>4.71%</t>
         </is>
       </c>
       <c r="F24" s="6" t="n">
-        <v>5.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -17608,14 +17608,14 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1030</v>
+        <v>1055</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1555</v>
+        <v>1582</v>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>2082 Views</t>
+          <t>2245 Views</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -17639,11 +17639,11 @@
         <v>522</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>999 Views</t>
+          <t>1015 Views</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -17660,18 +17660,18 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>/ernika/</t>
+          <t>/eka/</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>592</v>
+        <v>733</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>684</v>
+        <v>812</v>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>951 Views</t>
+          <t>907 Views</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -17688,18 +17688,18 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>/eka/</t>
+          <t>/ernika/</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>707</v>
+        <v>539</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>797</v>
+        <v>645</v>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>899 Views</t>
+          <t>907 Views</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -17720,14 +17720,14 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>630</v>
+        <v>540</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>683</v>
+        <v>584</v>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>676 Views</t>
+          <t>580 Views</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -17744,18 +17744,18 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>/about-us/</t>
+          <t>/blog/vastu-home-direction/is-a-south-facing-house-good-for-you-vastu-lifestyle-benefits/</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>187</v>
+        <v>374</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>280</v>
+        <v>426</v>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>366 Views</t>
+          <t>433 Views</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -17772,18 +17772,18 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>/residential-project/</t>
+          <t>/about-us/</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>351 Views</t>
+          <t>341 Views</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -17800,18 +17800,18 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>/how-to-check-property-ownership-in-bangalore/</t>
+          <t>/blog/</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>304</v>
+        <v>56</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>332</v>
+        <v>118</v>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>349 Views</t>
+          <t>285 Views</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -17828,18 +17828,18 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>/blog/vastu-home-direction/is-a-south-facing-house-good-for-you-vastu-lifestyle-benefits/</t>
+          <t>/residential-project/</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>286</v>
+        <v>203</v>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>292 Views</t>
+          <t>284 Views</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -17856,18 +17856,18 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>/elegance/</t>
+          <t>/how-to-check-property-ownership-in-bangalore/</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>141</v>
+        <v>228</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>277 Views</t>
+          <t>267 Views</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -17884,18 +17884,18 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>/north-facing-house-good-or-bad-according-to-vastu-shastra/</t>
+          <t>/contact-us/</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>236</v>
+        <v>147</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>269 Views</t>
+          <t>253 Views</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -17912,18 +17912,18 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>/contact-us/</t>
+          <t>/elegance/</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>204</v>
+        <v>163</v>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>242 Views</t>
+          <t>233 Views</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -17940,18 +17940,18 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>/saleable-area-vs-carpet-area-vs-built-up-area-explained/</t>
+          <t>/blog/property-buying-guide/how-to-check-property-ownership-in-bangalore/</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>14</v>
+        <v>199</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>27</v>
+        <v>225</v>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>209 Views</t>
+          <t>232 Views</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -17968,18 +17968,18 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>/blog/</t>
+          <t>/north-facing-house-good-or-bad-according-to-vastu-shastra/</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>52</v>
+        <v>196</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>199 Views</t>
+          <t>220 Views</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -17996,18 +17996,18 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>/kaveri-online-services-portal-a-complete-guide/</t>
+          <t>/saleable-area-vs-carpet-area-vs-built-up-area-explained/</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>165</v>
+        <v>27</v>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>178 Views</t>
+          <t>209 Views</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -18024,18 +18024,18 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>/how-to-check-rera-registered-projects-in-bangalore/</t>
+          <t>/our-projects/residential/</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>150 Views</t>
+          <t>202 Views</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -18052,18 +18052,18 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>/our-projects/residential/</t>
+          <t>/our-projects/villas/elegance/</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>143 Views</t>
+          <t>176 Views</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -18080,18 +18080,18 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>/shyam-residency/</t>
+          <t>/blog/vastu-home-direction/north-facing-house-good-or-bad-according-to-vastu-shastra/</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>48</v>
+        <v>156</v>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>134 Views</t>
+          <t>157 Views</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -18108,18 +18108,18 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>/blog/property-buying-guide/how-to-check-property-ownership-in-bangalore/</t>
+          <t>/how-to-check-rera-registered-projects-in-bangalore/</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>123 Views</t>
+          <t>125 Views</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -18136,18 +18136,18 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>/our-projects/villas/elegance/</t>
+          <t>/shyam-residency/</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>121 Views</t>
+          <t>117 Views</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -18168,10 +18168,10 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>3010</v>
+        <v>3129</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>3809</v>
+        <v>3953</v>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
@@ -18196,10 +18196,10 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1149</v>
+        <v>1125</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>1268</v>
+        <v>1251</v>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
@@ -18224,10 +18224,10 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>634</v>
+        <v>726</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>869</v>
+        <v>971</v>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
@@ -18252,10 +18252,10 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
@@ -18276,14 +18276,14 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Unassigned</t>
+          <t>Referral</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
@@ -18308,10 +18308,10 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
@@ -18332,14 +18332,14 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>Unassigned</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
@@ -18364,10 +18364,10 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - 30-DAY ACTION PLAN (Updated: 2026-09-26 12:50:54)</t>
+          <t>GURU PUNVAANII PROPERTIES - 30-DAY ACTION PLAN (Updated: 2026-09-29 12:05:18)</t>
         </is>
       </c>
     </row>
@@ -18777,9 +18777,9 @@
           <t>Content Team</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - WEEKLY PERFORMANCE TRACKING (Updated: 2026-09-26 12:50:54)</t>
+          <t>GURU PUNVAANII PROPERTIES - WEEKLY PERFORMANCE TRACKING (Updated: 2026-09-29 12:05:18)</t>
         </is>
       </c>
     </row>
@@ -18940,7 +18940,7 @@
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-26 12:49:34</t>
+          <t>2026-09-29 11:59:40</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">

--- a/Guru_Punvaanii_Complete_SEO_Audit_Report.xlsx
+++ b/Guru_Punvaanii_Complete_SEO_Audit_Report.xlsx
@@ -550,7 +550,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - EXECUTIVE SUMMARY (Updated: 2026-09-29 12:05:18)</t>
+          <t>GURU PUNVAANII PROPERTIES - EXECUTIVE SUMMARY (Updated: 2026-09-29 12:17:24)</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - TECHNICAL SEO (Updated: 2026-09-29 12:05:18)</t>
+          <t>GURU PUNVAANII PROPERTIES - TECHNICAL SEO (Updated: 2026-09-29 12:17:24)</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - ON-PAGE SEO (Updated: 2026-09-29 12:05:18)</t>
+          <t>GURU PUNVAANII PROPERTIES - ON-PAGE SEO (Updated: 2026-09-29 12:17:24)</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - SCHEMA &amp; STRUCTURED DATA (Updated: 2026-09-29 12:05:18)</t>
+          <t>GURU PUNVAANII PROPERTIES - SCHEMA &amp; STRUCTURED DATA (Updated: 2026-09-29 12:17:24)</t>
         </is>
       </c>
     </row>
@@ -12679,7 +12679,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - CORE WEB VITALS (Updated: 2026-09-29 12:05:18)</t>
+          <t>GURU PUNVAANII PROPERTIES - CORE WEB VITALS (Updated: 2026-09-29 12:17:24)</t>
         </is>
       </c>
     </row>
@@ -16798,7 +16798,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - IMAGE SEO &amp; ALT TAGS (Updated: 2026-09-29 12:05:18)</t>
+          <t>GURU PUNVAANII PROPERTIES - IMAGE SEO &amp; ALT TAGS (Updated: 2026-09-29 12:17:24)</t>
         </is>
       </c>
     </row>
@@ -16984,7 +16984,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - GSC &amp; GA4 LIVE DATA (Updated: 2026-09-29 12:05:18)</t>
+          <t>GURU PUNVAANII PROPERTIES - GSC &amp; GA4 LIVE DATA (Updated: 2026-09-29 12:17:24)</t>
         </is>
       </c>
     </row>
@@ -18409,7 +18409,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - 30-DAY ACTION PLAN (Updated: 2026-09-29 12:05:18)</t>
+          <t>GURU PUNVAANII PROPERTIES - 30-DAY ACTION PLAN (Updated: 2026-09-29 12:17:24)</t>
         </is>
       </c>
     </row>
@@ -18851,7 +18851,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GURU PUNVAANII PROPERTIES - WEEKLY PERFORMANCE TRACKING (Updated: 2026-09-29 12:05:18)</t>
+          <t>GURU PUNVAANII PROPERTIES - WEEKLY PERFORMANCE TRACKING (Updated: 2026-09-29 12:17:24)</t>
         </is>
       </c>
     </row>
